--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>118622712</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,6 +1030,118 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121401505</v>
+      </c>
+      <c r="B5" t="n">
+        <v>105186</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>s k "Storskogen" Brännbergsvägen, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>566215</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6807271</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2013-07-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>skogen nu avverkad, hittade en bladrosett, ingen blomma 2024</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Leif Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Leif Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>121401505</v>
       </c>
       <c r="B5" t="n">
-        <v>105186</v>
+        <v>105199</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>121401505</v>
       </c>
       <c r="B5" t="n">
-        <v>105199</v>
+        <v>105200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>121401505</v>
       </c>
       <c r="B5" t="n">
-        <v>105200</v>
+        <v>105203</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>121401505</v>
       </c>
       <c r="B5" t="n">
-        <v>105203</v>
+        <v>105209</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>121401505</v>
       </c>
       <c r="B5" t="n">
-        <v>105209</v>
+        <v>105210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -1035,7 +1035,7 @@
         <v>121401505</v>
       </c>
       <c r="B5" t="n">
-        <v>105210</v>
+        <v>105218</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>122185674</v>
       </c>
       <c r="B6" t="n">
-        <v>56287</v>
+        <v>56292</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -1162,11 +1162,6 @@
       <c r="E6" t="n">
         <v>206002</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Brunlångöra</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Plecotus auritus</t>

--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>122185674</v>
       </c>
       <c r="B6" t="n">
-        <v>56292</v>
+        <v>56296</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,6 +1161,11 @@
       </c>
       <c r="E6" t="n">
         <v>206002</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118622712</v>
+        <v>122185674</v>
       </c>
       <c r="B4" t="n">
-        <v>97858</v>
+        <v>56296</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,39 +929,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>206002</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -999,12 +992,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>i ugglenät</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,7 +1011,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1029,230 +1026,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>121401505</v>
-      </c>
-      <c r="B5" t="n">
-        <v>105218</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>s k "Storskogen" Brännbergsvägen, Hls</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>566215</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6807271</v>
-      </c>
-      <c r="S5" t="n">
-        <v>100</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Bollnäs</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Bollnäs</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2013-07-15</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2013-07-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>skogen nu avverkad, hittade en bladrosett, ingen blomma 2024</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Leif Larsson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Leif Larsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>122185674</v>
-      </c>
-      <c r="B6" t="n">
-        <v>56296</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>206002</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Brunlångöra</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Plecotus auritus</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>s k "Storskogen" Brännbergsvägen, Hls</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>566215</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6807271</v>
-      </c>
-      <c r="S6" t="n">
-        <v>100</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Bollnäs</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Bollnäs</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>i ugglenät</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Leif Larsson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Leif Larsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -675,47 +675,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101837322</v>
+        <v>122185674</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>206002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566214.4289120134</v>
+        <v>566215</v>
       </c>
       <c r="R2" t="n">
-        <v>6807270.952684764</v>
+        <v>6807271</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -753,22 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>i ugglenät</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,44 +782,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101837511</v>
+        <v>60728622</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -844,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566214.4289120134</v>
+        <v>566215</v>
       </c>
       <c r="R3" t="n">
-        <v>6807270.952684764</v>
+        <v>6807271</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -874,22 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,44 +888,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122185674</v>
+        <v>101837511</v>
       </c>
       <c r="B4" t="n">
-        <v>56296</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206002</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -992,17 +961,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>i ugglenät</t>
+          <t>2022-06-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,6 +975,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 43259-2021 artfynd.xlsx
+++ b/artfynd/A 43259-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122185674</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60728622</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,8 +1006,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101837511</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>